--- a/output/pdf_financials_xlsx/RECE.xlsx
+++ b/output/pdf_financials_xlsx/RECE.xlsx
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.052184</v>
+        <v>0.278384</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.019396</v>
+        <v>0.187737</v>
       </c>
     </row>
     <row r="11">
@@ -566,10 +566,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.052184</v>
+        <v>-0.278384</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.019396</v>
+        <v>-0.187737</v>
       </c>
     </row>
     <row r="12">
@@ -579,7 +579,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.001404</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.280127</v>
+        <v>-0.281531</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-0.202154</v>
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.280127</v>
+        <v>-0.281531</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-0.202154</v>
@@ -887,10 +887,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.022484</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.00132</v>
       </c>
     </row>
     <row r="35">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.022484</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.00132</v>
       </c>
     </row>
     <row r="37">
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.049815</v>
+        <v>0.027331</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.018651</v>
+        <v>0.017331</v>
       </c>
     </row>
     <row r="49">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">

--- a/output/pdf_financials_xlsx/RECE.xlsx
+++ b/output/pdf_financials_xlsx/RECE.xlsx
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.021818</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.0095</v>
       </c>
     </row>
     <row r="68">
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.015637</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.01176</v>
       </c>
     </row>
     <row r="111">
@@ -2822,7 +2822,11 @@
           <t>Accrued interest and accretion expense</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="n">
         <v>0.015637</v>
       </c>
@@ -3008,7 +3012,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
